--- a/results/Int Task Remove ACC 0.1/Rando_fi_explain.xlsx
+++ b/results/Int Task Remove ACC 0.1/Rando_fi_explain.xlsx
@@ -1148,268 +1148,268 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0006663317009561565</v>
+        <v>-0.001575729779221117</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.002168289863660566</v>
+        <v>-0.002092648123638018</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0004829699412271072</v>
+        <v>-0.001935355716052384</v>
       </c>
       <c r="F3" t="n">
-        <v>0.001039488449256349</v>
+        <v>0.001682486889122277</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0002168324626607542</v>
+        <v>6.978285967238919e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>0.001235514787464884</v>
+        <v>0.002882637613156113</v>
       </c>
       <c r="I3" t="n">
-        <v>1.231664241591046e-05</v>
+        <v>0.0001825435843891521</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0003693730923731275</v>
+        <v>-0.003270121928090064</v>
       </c>
       <c r="K3" t="n">
-        <v>0.02518001305659089</v>
+        <v>0.0166426452228114</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02547558928319565</v>
+        <v>0.02745946902362753</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0003060916817080072</v>
+        <v>0.001333612468686893</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.002371280366106883</v>
+        <v>-0.0001826434420665402</v>
       </c>
       <c r="O3" t="n">
-        <v>0.002437240908866181</v>
+        <v>0.002470032367333981</v>
       </c>
       <c r="P3" t="n">
-        <v>0.007230233544349238</v>
+        <v>0.01095467714603303</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.005485910532002368</v>
+        <v>0.005322899993649386</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.001378862737973638</v>
+        <v>-0.002701008269559943</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.001777102433378637</v>
+        <v>-0.00175128112286069</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.0006802098482790234</v>
+        <v>-0.0007038315496301439</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.001080179644057423</v>
+        <v>-0.0007336924869568206</v>
       </c>
       <c r="V3" t="n">
-        <v>0.000120949874835653</v>
+        <v>8.138360010660928e-05</v>
       </c>
       <c r="W3" t="n">
-        <v>0.002435109637252847</v>
+        <v>0.0006792313120660699</v>
       </c>
       <c r="X3" t="n">
-        <v>0.001330838103490525</v>
+        <v>0.001901720239149313</v>
       </c>
       <c r="Y3" t="n">
-        <v>-0.0002068318478913589</v>
+        <v>-0.0007545097302136694</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.0004111686659228619</v>
+        <v>-0.0005231447020443159</v>
       </c>
       <c r="AA3" t="n">
-        <v>-6.315455117891332e-06</v>
+        <v>0.0006613505443953116</v>
       </c>
       <c r="AB3" t="n">
-        <v>3.532473606645105e-05</v>
+        <v>0.0002252957977065451</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.001561981046808213</v>
+        <v>0.002515258497091486</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.0006956958418329106</v>
+        <v>0.001377917280592464</v>
       </c>
       <c r="AE3" t="n">
-        <v>-0.0002194207638392242</v>
+        <v>0.0008889530077325801</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.001963016676876267</v>
+        <v>0.001993738283859832</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.0001398165996662415</v>
+        <v>0.0002811768843623308</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.0001422237609054078</v>
+        <v>-3.081492353254165e-05</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.002684181376090456</v>
+        <v>0.0009431252628769096</v>
       </c>
       <c r="AK3" t="n">
-        <v>-0.0004801775463632353</v>
+        <v>-0.0003062164673702717</v>
       </c>
       <c r="AL3" t="n">
-        <v>-0.0001100605823043255</v>
+        <v>-0.0004718545157731801</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.0001359992704219137</v>
+        <v>0.0004100316986147468</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.0003203176180389177</v>
+        <v>-0.001006682419322097</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.0009605907867540377</v>
+        <v>0.0004629972223955635</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.0003935159459175008</v>
+        <v>0.0001752331508842753</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-0.0006069637358073468</v>
+        <v>-9.578007896754448e-06</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.001558115263928068</v>
+        <v>-0.0005317135060677947</v>
       </c>
       <c r="AS3" t="n">
-        <v>-0.001662443366366606</v>
+        <v>-0.002559697359831006</v>
       </c>
       <c r="AT3" t="n">
-        <v>-0.001704965373530176</v>
+        <v>-0.002849595596501444</v>
       </c>
       <c r="AU3" t="n">
-        <v>-0.0004446070484053778</v>
+        <v>-0.0005722122434440903</v>
       </c>
       <c r="AV3" t="n">
-        <v>-2.932875226315574e-05</v>
+        <v>-0.0005623060390729162</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.001043548529548268</v>
+        <v>0.0009459017280672334</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.0002374965223850578</v>
+        <v>9.799816696491549e-05</v>
       </c>
       <c r="AY3" t="n">
-        <v>0.001828169921431001</v>
+        <v>-0.00101668161767569</v>
       </c>
       <c r="AZ3" t="n">
-        <v>-0.002308878959087806</v>
+        <v>-0.002684055005143962</v>
       </c>
       <c r="BA3" t="n">
-        <v>-0.00512972128339924</v>
+        <v>-0.005346323304025602</v>
       </c>
       <c r="BB3" t="n">
-        <v>-0.003142594150092092</v>
+        <v>-0.005995071341458808</v>
       </c>
       <c r="BC3" t="n">
-        <v>0.0004734280641560351</v>
+        <v>0.0005802697894428031</v>
       </c>
       <c r="BD3" t="n">
-        <v>-0.0005467794428731821</v>
+        <v>0.0002028816620523566</v>
       </c>
       <c r="BE3" t="n">
-        <v>-0.0003901332456692264</v>
+        <v>-1.246274474824282e-06</v>
       </c>
       <c r="BF3" t="n">
-        <v>-0.001245569977496848</v>
+        <v>-0.003188194372361984</v>
       </c>
       <c r="BG3" t="n">
-        <v>-0.003441078332680419</v>
+        <v>-0.002304197382528158</v>
       </c>
       <c r="BH3" t="n">
-        <v>0</v>
+        <v>3.650967506390046e-05</v>
       </c>
       <c r="BI3" t="n">
-        <v>-0.000118500093098498</v>
+        <v>0.0001171003509331437</v>
       </c>
       <c r="BJ3" t="n">
-        <v>-0.002582163133438936</v>
+        <v>-0.0003469091529726477</v>
       </c>
       <c r="BK3" t="n">
-        <v>-0.006665207130260987</v>
+        <v>-0.001588319992108411</v>
       </c>
       <c r="BL3" t="n">
-        <v>-0.0001101699696820846</v>
+        <v>5.849865706103241e-05</v>
       </c>
       <c r="BM3" t="n">
-        <v>-0.002098572422899579</v>
+        <v>0.0002369759231655533</v>
       </c>
       <c r="BN3" t="n">
-        <v>-0.002691051900271376</v>
+        <v>-0.002468230598326916</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.001402857716990817</v>
+        <v>0.0005331670868464467</v>
       </c>
       <c r="BP3" t="n">
-        <v>-0.002696036273265832</v>
+        <v>-0.001256894618499336</v>
       </c>
       <c r="BQ3" t="n">
-        <v>-0.0001509544137582841</v>
+        <v>0.0001286671104615922</v>
       </c>
       <c r="BR3" t="n">
-        <v>0.001283077712401358</v>
+        <v>-0.001455086874587316</v>
       </c>
       <c r="BS3" t="n">
-        <v>-0.001487038472053354</v>
+        <v>4.209939956637413e-05</v>
       </c>
       <c r="BT3" t="n">
-        <v>-3.393051051849502e-05</v>
+        <v>0.0005205504229248525</v>
       </c>
       <c r="BU3" t="n">
-        <v>0.00460721547512366</v>
+        <v>0.002370603437629648</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.0009332480312196646</v>
+        <v>6.775962318346664e-05</v>
       </c>
       <c r="BW3" t="n">
-        <v>0.0005428354387489798</v>
+        <v>0.002731374499676855</v>
       </c>
       <c r="BX3" t="n">
-        <v>5.483925833431381e-05</v>
+        <v>-8.216666815986541e-05</v>
       </c>
       <c r="BY3" t="n">
-        <v>0.0005845181666766652</v>
+        <v>0.000440020815530866</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0.0007694013614956952</v>
+        <v>0.000421153440877785</v>
       </c>
       <c r="CA3" t="n">
-        <v>5.059212129805091e-05</v>
+        <v>1.632653061224509e-05</v>
       </c>
       <c r="CB3" t="n">
-        <v>0.0001535370653612489</v>
+        <v>0.0009696076556062529</v>
       </c>
       <c r="CC3" t="n">
-        <v>0.002376440152030338</v>
+        <v>0.00119593290197717</v>
       </c>
       <c r="CD3" t="n">
-        <v>-0.0001933698148111662</v>
+        <v>-8.163265306120327e-06</v>
       </c>
       <c r="CE3" t="n">
-        <v>0.000877001987575371</v>
+        <v>0.001068027434624737</v>
       </c>
       <c r="CF3" t="n">
-        <v>-0.001728252787888224</v>
+        <v>0.0008504369692680581</v>
       </c>
       <c r="CG3" t="n">
-        <v>-0.0002422912434632096</v>
+        <v>-0.0004972173861459239</v>
       </c>
       <c r="CH3" t="n">
-        <v>-0.0002433408237166935</v>
+        <v>0.000369710321672584</v>
       </c>
       <c r="CI3" t="n">
-        <v>0.001258000629196709</v>
+        <v>0.002409210223196103</v>
       </c>
       <c r="CJ3" t="n">
-        <v>0.0007166441253393693</v>
+        <v>8.674050185683135e-05</v>
       </c>
       <c r="CK3" t="n">
-        <v>-0.001007743624935691</v>
+        <v>0.001107431544162769</v>
       </c>
     </row>
     <row r="4">
@@ -1419,268 +1419,268 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.003651031344206028</v>
+        <v>0.002674213243279293</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>0.007408739562709931</v>
+        <v>0.008196877935105987</v>
       </c>
       <c r="E4" t="n">
-        <v>0.003666795933107507</v>
+        <v>0.003583988424596452</v>
       </c>
       <c r="F4" t="n">
-        <v>0.007013988342765862</v>
+        <v>0.00640559894146441</v>
       </c>
       <c r="G4" t="n">
-        <v>0.005159929682794154</v>
+        <v>0.005971845410115465</v>
       </c>
       <c r="H4" t="n">
-        <v>0.004511394592200635</v>
+        <v>0.007705008605145298</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0004177765250454891</v>
+        <v>0.0004389969848607782</v>
       </c>
       <c r="J4" t="n">
-        <v>0.00875035806553994</v>
+        <v>0.009414816335565557</v>
       </c>
       <c r="K4" t="n">
-        <v>0.02273208956014856</v>
+        <v>0.01887135861838446</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02700729338999942</v>
+        <v>0.02812863564191136</v>
       </c>
       <c r="M4" t="n">
-        <v>0.00670377566228914</v>
+        <v>0.007829061502178216</v>
       </c>
       <c r="N4" t="n">
-        <v>0.004343300412944519</v>
+        <v>0.006561153080316151</v>
       </c>
       <c r="O4" t="n">
-        <v>0.003673166178327999</v>
+        <v>0.005881597770650553</v>
       </c>
       <c r="P4" t="n">
-        <v>0.01912910538391317</v>
+        <v>0.01705163315257191</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.01425872658170795</v>
+        <v>0.01633925471110566</v>
       </c>
       <c r="R4" t="n">
-        <v>0.006745908282430957</v>
+        <v>0.009304833629535939</v>
       </c>
       <c r="S4" t="n">
-        <v>0.003800299199205132</v>
+        <v>0.002906344724167758</v>
       </c>
       <c r="T4" t="n">
-        <v>0.005561466159758624</v>
+        <v>0.007513769557925978</v>
       </c>
       <c r="U4" t="n">
-        <v>0.004627402472899571</v>
+        <v>0.003285990399271763</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0003768929719465867</v>
+        <v>0.0002792165502052127</v>
       </c>
       <c r="W4" t="n">
-        <v>0.01037657494904518</v>
+        <v>0.01010616033018135</v>
       </c>
       <c r="X4" t="n">
-        <v>0.006814148480855246</v>
+        <v>0.006166849089144053</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.003479778572011284</v>
+        <v>0.00411806004563718</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.002164802241407159</v>
+        <v>0.002404952712713659</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.004796702719791449</v>
+        <v>0.003987669112789306</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.0006165336950976455</v>
+        <v>0.0008613511892856941</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.0085651130407382</v>
+        <v>0.01024734937379584</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.008174636554970584</v>
+        <v>0.007972331348389991</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.007701403362786834</v>
+        <v>0.005417771745489133</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.009692649186677055</v>
+        <v>0.008505104522868175</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.0008001897286683953</v>
+        <v>0.0006259098780424422</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.0009054238388574692</v>
+        <v>0.001288527463005846</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.007427554067110548</v>
+        <v>0.009705325679488917</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.01029634215618706</v>
+        <v>0.007243061359346205</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.0008682776007256488</v>
+        <v>0.0008819877176013827</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.0009292560523680457</v>
+        <v>0.001902198928672034</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.00379884730971614</v>
+        <v>0.004964720684067214</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.005774994474634738</v>
+        <v>0.007761810323731158</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.001196786066418165</v>
+        <v>0.0009772884843646777</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.004772180577646424</v>
+        <v>0.003066442770291322</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.006965334460998051</v>
+        <v>0.006010049597805218</v>
       </c>
       <c r="AS4" t="n">
-        <v>0.004047473409932441</v>
+        <v>0.002891703185673987</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.006696256748307663</v>
+        <v>0.006760840473082948</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.01140439966071357</v>
+        <v>0.009715386554637828</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.003750165586884914</v>
+        <v>0.002018142758110152</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.005214272465926166</v>
+        <v>0.004823754432341098</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.0005793775336560051</v>
+        <v>0.0005716254916889014</v>
       </c>
       <c r="AY4" t="n">
-        <v>0.004985705976971721</v>
+        <v>0.003182228161122952</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.006510561418974712</v>
+        <v>0.007625142895513547</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.01209741444366895</v>
+        <v>0.01239344689370336</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.006365015483840505</v>
+        <v>0.00779733157124394</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.001318313245304515</v>
+        <v>0.001158240820986665</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.000838905856847712</v>
+        <v>0.001579274800838395</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.0006241009128502534</v>
+        <v>0.0005006252976734465</v>
       </c>
       <c r="BF4" t="n">
-        <v>0.007590355756279633</v>
+        <v>0.00647128816119823</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.0128244010445459</v>
+        <v>0.008939868267723871</v>
       </c>
       <c r="BH4" t="n">
-        <v>0</v>
+        <v>0.000115453729834579</v>
       </c>
       <c r="BI4" t="n">
-        <v>0.0007633857884285226</v>
+        <v>0.001071024491218231</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.00498095442756807</v>
+        <v>0.003035821544005478</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.005720151847727097</v>
+        <v>0.00679237407210734</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.0007328607371012889</v>
+        <v>0.001462613673235391</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.004782757551917827</v>
+        <v>0.005513149727747309</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.005749862689374185</v>
+        <v>0.009470162099316618</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.006630706294688841</v>
+        <v>0.003822327271245153</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.006503500663143287</v>
+        <v>0.005104707491796729</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0.0006791948035157565</v>
+        <v>0.0004582517621109165</v>
       </c>
       <c r="BR4" t="n">
-        <v>0.009124659805525589</v>
+        <v>0.003824371667982432</v>
       </c>
       <c r="BS4" t="n">
-        <v>0.004729656206260294</v>
+        <v>0.00509593373337675</v>
       </c>
       <c r="BT4" t="n">
-        <v>0.00201860427235972</v>
+        <v>0.001764502543473374</v>
       </c>
       <c r="BU4" t="n">
-        <v>0.01038130652619127</v>
+        <v>0.01119869616580656</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.004051848884699002</v>
+        <v>0.003663081476729075</v>
       </c>
       <c r="BW4" t="n">
-        <v>0.01100370356831932</v>
+        <v>0.007406933697491282</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.0003692260803770969</v>
+        <v>0.0002282508680147976</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.001817078851368845</v>
+        <v>0.0009661193223125128</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.001323286279066254</v>
+        <v>0.001489140293719131</v>
       </c>
       <c r="CA4" t="n">
-        <v>0.0001394517143178925</v>
+        <v>5.162902302315783e-05</v>
       </c>
       <c r="CB4" t="n">
-        <v>0.001882190644359653</v>
+        <v>0.0009631323998035552</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.008932269243019167</v>
+        <v>0.008305210264176889</v>
       </c>
       <c r="CD4" t="n">
-        <v>0.0007949797776675954</v>
+        <v>2.58145115115719e-05</v>
       </c>
       <c r="CE4" t="n">
-        <v>0.001774273928350446</v>
+        <v>0.001495378862003212</v>
       </c>
       <c r="CF4" t="n">
-        <v>0.005551226142369427</v>
+        <v>0.005481494511608959</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.004837649445198093</v>
+        <v>0.006666044613309605</v>
       </c>
       <c r="CH4" t="n">
-        <v>0.001653295440398822</v>
+        <v>0.00125770160266614</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.004990688326564709</v>
+        <v>0.002897651700685289</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0.006467706775455342</v>
+        <v>0.00817412751459771</v>
       </c>
       <c r="CK4" t="n">
-        <v>0.002576192067727583</v>
+        <v>0.002586766223156124</v>
       </c>
     </row>
     <row r="5">
@@ -1690,268 +1690,268 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.00560061799922752</v>
+        <v>-0.006160616061606128</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.01738775510204085</v>
+        <v>-0.02134693877551014</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.005707762557077678</v>
+        <v>-0.007228915662650548</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.009073506891271</v>
+        <v>-0.009974330766409956</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.008497489378138313</v>
+        <v>-0.0080339899575125</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.006123945727906155</v>
+        <v>-0.01140447378071137</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.0006466337010269996</v>
+        <v>-0.000330033003300334</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.01936193619361941</v>
+        <v>-0.02750275027502749</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.01371185786017771</v>
+        <v>-0.02406334492081881</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.02058709926612594</v>
+        <v>-0.03310158362302044</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.01706016755521705</v>
+        <v>-0.01584158415841583</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.01247585940517578</v>
+        <v>-0.01062431544359251</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.004143747708104173</v>
+        <v>-0.008874220755408835</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.03680175246440304</v>
+        <v>-0.02037239868565165</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.01500547645125956</v>
+        <v>-0.02402336619204084</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.01672167216721676</v>
+        <v>-0.0277227722772277</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.007493240633449217</v>
+        <v>-0.005287181437808997</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.01085441877521089</v>
+        <v>-0.01279794646131278</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.009192738509076903</v>
+        <v>-0.004928806133625374</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.0005476451259583404</v>
+        <v>-0.0003423354887789998</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.01861993428258486</v>
+        <v>-0.02322015334063522</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.01149162861491633</v>
+        <v>-0.005631659056316596</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.009017889740781271</v>
+        <v>-0.009800918836140916</v>
       </c>
       <c r="Z5" t="n">
-        <v>-0.004855786783497584</v>
+        <v>-0.004740235115661707</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0.01270536692223436</v>
+        <v>-0.007374954362906116</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0.0008111239860950304</v>
+        <v>-0.001255707762557079</v>
       </c>
       <c r="AC5" t="n">
-        <v>-0.01361810879883166</v>
+        <v>-0.01296093464768158</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0.01230007616146229</v>
+        <v>-0.006125574272588074</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0.01647640791476412</v>
+        <v>-0.003691019786910199</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.009130913091309156</v>
+        <v>-0.01576824349101573</v>
       </c>
       <c r="AG5" t="n">
-        <v>-0.0009893455098935022</v>
+        <v>-0.0008421052631578773</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0.001217192848991999</v>
+        <v>-0.002394747006566211</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0.006584992343032114</v>
+        <v>-0.01529152915291526</v>
       </c>
       <c r="AK5" t="n">
-        <v>-0.01275704493526275</v>
+        <v>-0.009433244579688072</v>
       </c>
       <c r="AL5" t="n">
-        <v>-0.002240247199691014</v>
+        <v>-0.001980198019801949</v>
       </c>
       <c r="AM5" t="n">
-        <v>-0.001306122448979607</v>
+        <v>-0.003412969283276424</v>
       </c>
       <c r="AN5" t="n">
-        <v>-0.008287696239503451</v>
+        <v>-0.009188361408882096</v>
       </c>
       <c r="AO5" t="n">
-        <v>-0.009741248097412513</v>
+        <v>-0.01700913242009132</v>
       </c>
       <c r="AP5" t="n">
-        <v>-0.001175578308684166</v>
+        <v>-0.001087719298245604</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-0.009163928441036839</v>
+        <v>-0.005878057685286553</v>
       </c>
       <c r="AR5" t="n">
-        <v>-0.007800608828006162</v>
+        <v>-0.00730593607305936</v>
       </c>
       <c r="AS5" t="n">
-        <v>-0.01036734693877552</v>
+        <v>-0.00964429776310961</v>
       </c>
       <c r="AT5" t="n">
-        <v>-0.01397396630934147</v>
+        <v>-0.01367346938775504</v>
       </c>
       <c r="AU5" t="n">
-        <v>-0.02789193302891937</v>
+        <v>-0.02119482496194824</v>
       </c>
       <c r="AV5" t="n">
-        <v>-0.008751902587519044</v>
+        <v>-0.004074638233054107</v>
       </c>
       <c r="AW5" t="n">
-        <v>-0.005390539053905419</v>
+        <v>-0.003884234577303913</v>
       </c>
       <c r="AX5" t="n">
-        <v>-0.0008771929824561098</v>
+        <v>-0.001225114854517639</v>
       </c>
       <c r="AY5" t="n">
-        <v>-0.004036557501904026</v>
+        <v>-0.007656967840735085</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-0.0127612761276128</v>
+        <v>-0.0162456140350877</v>
       </c>
       <c r="BA5" t="n">
-        <v>-0.03212244897959186</v>
+        <v>-0.03771428571428568</v>
       </c>
       <c r="BB5" t="n">
-        <v>-0.01039011201236002</v>
+        <v>-0.02179591836734687</v>
       </c>
       <c r="BC5" t="n">
-        <v>-0.001523229246001501</v>
+        <v>-0.001642935377875099</v>
       </c>
       <c r="BD5" t="n">
-        <v>-0.001368421052631563</v>
+        <v>-0.001898503103322313</v>
       </c>
       <c r="BE5" t="n">
-        <v>-0.00148514851485152</v>
+        <v>-0.0006846709775579996</v>
       </c>
       <c r="BF5" t="n">
-        <v>-0.01884897643877948</v>
+        <v>-0.01610660486674386</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.02863705972434914</v>
+        <v>-0.01673684210526313</v>
       </c>
       <c r="BH5" t="n">
         <v>0</v>
       </c>
       <c r="BI5" t="n">
-        <v>-0.001815372730784093</v>
+        <v>-0.001369341955115999</v>
       </c>
       <c r="BJ5" t="n">
-        <v>-0.008816326530612239</v>
+        <v>-0.003598774885145517</v>
       </c>
       <c r="BK5" t="n">
-        <v>-0.01400806747341405</v>
+        <v>-0.01160030627871365</v>
       </c>
       <c r="BL5" t="n">
-        <v>-0.001142857142857157</v>
+        <v>-0.001755102040816237</v>
       </c>
       <c r="BM5" t="n">
-        <v>-0.01103500761035014</v>
+        <v>-0.006278713629402788</v>
       </c>
       <c r="BN5" t="n">
-        <v>-0.01394360757049056</v>
+        <v>-0.01510204081632648</v>
       </c>
       <c r="BO5" t="n">
-        <v>-0.009589041095890437</v>
+        <v>-0.005422828972316995</v>
       </c>
       <c r="BP5" t="n">
-        <v>-0.01068147013782537</v>
+        <v>-0.008789954337899553</v>
       </c>
       <c r="BQ5" t="n">
-        <v>-0.002040816326530637</v>
+        <v>-0.0001754385964912175</v>
       </c>
       <c r="BR5" t="n">
-        <v>-0.01575342465753429</v>
+        <v>-0.01018376722817765</v>
       </c>
       <c r="BS5" t="n">
-        <v>-0.007957462412907979</v>
+        <v>-0.006773211567732107</v>
       </c>
       <c r="BT5" t="n">
-        <v>-0.002456140350877167</v>
+        <v>-0.001788974078130656</v>
       </c>
       <c r="BU5" t="n">
-        <v>-0.0112970711297071</v>
+        <v>-0.0115296803652968</v>
       </c>
       <c r="BV5" t="n">
-        <v>-0.00350076103500766</v>
+        <v>-0.004718417047184164</v>
       </c>
       <c r="BW5" t="n">
-        <v>-0.02073820395738208</v>
+        <v>-0.007229832572298334</v>
       </c>
       <c r="BX5" t="n">
-        <v>-0.0006566241792198002</v>
+        <v>-0.0003667033370003514</v>
       </c>
       <c r="BY5" t="n">
-        <v>-0.001940639269406452</v>
+        <v>-0.001438596491228061</v>
       </c>
       <c r="BZ5" t="n">
-        <v>-0.001065043742867999</v>
+        <v>-0.003087719298245595</v>
       </c>
       <c r="CA5" t="n">
-        <v>-0.0001137656427758871</v>
+        <v>0</v>
       </c>
       <c r="CB5" t="n">
-        <v>-0.003729071537290774</v>
+        <v>-0.0002456140350876934</v>
       </c>
       <c r="CC5" t="n">
-        <v>-0.008599695585996991</v>
+        <v>-0.01554364471669221</v>
       </c>
       <c r="CD5" t="n">
-        <v>-0.002408163265306151</v>
+        <v>-8.163265306120327e-05</v>
       </c>
       <c r="CE5" t="n">
-        <v>-0.0007227082540889995</v>
+        <v>-0.0007719298245613682</v>
       </c>
       <c r="CF5" t="n">
-        <v>-0.008035034272658014</v>
+        <v>-0.006453978731206433</v>
       </c>
       <c r="CG5" t="n">
-        <v>-0.008862685431723106</v>
+        <v>-0.01431852986217458</v>
       </c>
       <c r="CH5" t="n">
-        <v>-0.002896871378910793</v>
+        <v>-0.002549246813441442</v>
       </c>
       <c r="CI5" t="n">
-        <v>-0.007334066740007372</v>
+        <v>-0.001186830015313944</v>
       </c>
       <c r="CJ5" t="n">
-        <v>-0.007465543644716644</v>
+        <v>-0.011676875957121</v>
       </c>
       <c r="CK5" t="n">
-        <v>-0.005368421052631545</v>
+        <v>-0.002718223583460977</v>
       </c>
     </row>
     <row r="6">
@@ -1961,268 +1961,268 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.00136061047401318</v>
+        <v>-0.003048697907716807</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.004934060207640154</v>
+        <v>-0.002538604499075736</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.001362443936701374</v>
+        <v>-0.004912250763427314</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.002382527409367443</v>
+        <v>-0.001323867047247201</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.003044815244240534</v>
+        <v>-0.004407139431891913</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.00280180050344917</v>
+        <v>-0.002047280687541686</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.0002847251458849232</v>
+        <v>-0.0002222478028467784</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.001962933725407512</v>
+        <v>-0.003915061850119229</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01401362001428064</v>
+        <v>0.009352626991328808</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01776535808304993</v>
+        <v>0.01747227443691145</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0005373766290965309</v>
+        <v>-0.001427689135352636</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.004313852032976556</v>
+        <v>-0.002940901742410615</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.0007862268008177353</v>
+        <v>7.604232463153116e-05</v>
       </c>
       <c r="P6" t="n">
-        <v>0.001252503404630298</v>
+        <v>0.006195496832788291</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.004483368103471816</v>
+        <v>0.003264133944775274</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.002622822488617949</v>
+        <v>-0.002263055934312333</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.004330585105052861</v>
+        <v>-0.003832687247094704</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.002151540870428639</v>
+        <v>-0.005256186024018688</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.00328610772036112</v>
+        <v>-0.003415774230484239</v>
       </c>
       <c r="V6" t="n">
-        <v>-2.853881278541414e-05</v>
+        <v>-0.0001036593989319323</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.003152949219514151</v>
+        <v>-0.002088362839423616</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.001004977029096435</v>
+        <v>-0.001245658915722084</v>
       </c>
       <c r="Y6" t="n">
-        <v>-0.001007276426552378</v>
+        <v>-0.001006885815220629</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.5972027403397e-05</v>
+        <v>-0.001587142633614186</v>
       </c>
       <c r="AA6" t="n">
-        <v>-9.942838598850644e-05</v>
+        <v>-0.000768983680408597</v>
       </c>
       <c r="AB6" t="n">
-        <v>-0.000289448148981919</v>
+        <v>-7.627649537198245e-05</v>
       </c>
       <c r="AC6" t="n">
-        <v>-0.001165163921617657</v>
+        <v>-0.003463604326624234</v>
       </c>
       <c r="AD6" t="n">
-        <v>-0.003994600804708165</v>
+        <v>-0.003531286327013289</v>
       </c>
       <c r="AE6" t="n">
-        <v>-0.001878019254049667</v>
+        <v>-0.002390490651742217</v>
       </c>
       <c r="AF6" t="n">
-        <v>-0.004612517127428039</v>
+        <v>-0.002361227532844354</v>
       </c>
       <c r="AG6" t="n">
-        <v>-0.0001956287465481626</v>
+        <v>-2.85605483625162e-05</v>
       </c>
       <c r="AH6" t="n">
-        <v>-0.0003010151892382184</v>
+        <v>-0.0009473684210526078</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>-0.001621905791876985</v>
+        <v>-0.005964275355144846</v>
       </c>
       <c r="AK6" t="n">
-        <v>-0.006951033405431417</v>
+        <v>-0.005899466869763881</v>
       </c>
       <c r="AL6" t="n">
-        <v>-0.0002726535811476111</v>
+        <v>-0.000525659000375292</v>
       </c>
       <c r="AM6" t="n">
-        <v>-0.0005456370938298372</v>
+        <v>-0.0007964811637853897</v>
       </c>
       <c r="AN6" t="n">
-        <v>-0.001689252829392573</v>
+        <v>-0.003358618017073986</v>
       </c>
       <c r="AO6" t="n">
-        <v>-0.0005744578506433479</v>
+        <v>-0.00370433318635506</v>
       </c>
       <c r="AP6" t="n">
-        <v>-0.0002082815569006136</v>
+        <v>-0.000748427186043199</v>
       </c>
       <c r="AQ6" t="n">
-        <v>-0.002602885230982521</v>
+        <v>-0.001674038639188069</v>
       </c>
       <c r="AR6" t="n">
-        <v>-0.003917284945358779</v>
+        <v>-0.006175755695489473</v>
       </c>
       <c r="AS6" t="n">
-        <v>-0.00142472281470376</v>
+        <v>-0.003313377109567348</v>
       </c>
       <c r="AT6" t="n">
-        <v>-0.006229319031366853</v>
+        <v>-0.008771389419643694</v>
       </c>
       <c r="AU6" t="n">
-        <v>-0.004149193958244365</v>
+        <v>-0.002962559975442564</v>
       </c>
       <c r="AV6" t="n">
-        <v>-0.001539929529169723</v>
+        <v>-0.001235410717173338</v>
       </c>
       <c r="AW6" t="n">
-        <v>-0.00374460308893797</v>
+        <v>-0.002188990025535018</v>
       </c>
       <c r="AX6" t="n">
-        <v>-1.578347727447527e-05</v>
+        <v>-0.0001272550435598568</v>
       </c>
       <c r="AY6" t="n">
-        <v>-0.001473657639736628</v>
+        <v>-0.002626841182411713</v>
       </c>
       <c r="AZ6" t="n">
-        <v>-0.006239952636344692</v>
+        <v>-0.005719387199764103</v>
       </c>
       <c r="BA6" t="n">
-        <v>-0.008850441036669991</v>
+        <v>-0.005226623521925503</v>
       </c>
       <c r="BB6" t="n">
-        <v>-0.008485257772352615</v>
+        <v>-0.009628790404080476</v>
       </c>
       <c r="BC6" t="n">
-        <v>-0.0002435973230543648</v>
+        <v>0.0001089578357415188</v>
       </c>
       <c r="BD6" t="n">
-        <v>-0.00110815298397311</v>
+        <v>-0.0009929966863856943</v>
       </c>
       <c r="BE6" t="n">
-        <v>-0.0007107388821074312</v>
+        <v>-0.0003341246405342086</v>
       </c>
       <c r="BF6" t="n">
-        <v>-0.003094377858838493</v>
+        <v>-0.004873147889292695</v>
       </c>
       <c r="BG6" t="n">
-        <v>-0.009793403044390756</v>
+        <v>-0.009755799345353163</v>
       </c>
       <c r="BH6" t="n">
         <v>0</v>
       </c>
       <c r="BI6" t="n">
-        <v>-0.0003794967971462643</v>
+        <v>-0.0002284409157459588</v>
       </c>
       <c r="BJ6" t="n">
-        <v>-0.006221239023077932</v>
+        <v>-0.003122025848527962</v>
       </c>
       <c r="BK6" t="n">
-        <v>-0.01101208707066288</v>
+        <v>-0.007423042820633116</v>
       </c>
       <c r="BL6" t="n">
-        <v>-0.0006952713659385851</v>
+        <v>-0.0007093456785951413</v>
       </c>
       <c r="BM6" t="n">
-        <v>-0.004257664840579916</v>
+        <v>-0.003702644966781865</v>
       </c>
       <c r="BN6" t="n">
-        <v>-0.004526750043425426</v>
+        <v>-0.01015063947918634</v>
       </c>
       <c r="BO6" t="n">
-        <v>-0.001413218244901443</v>
+        <v>-0.001736647711643533</v>
       </c>
       <c r="BP6" t="n">
-        <v>-0.007733860228128067</v>
+        <v>-0.005198932712441762</v>
       </c>
       <c r="BQ6" t="n">
-        <v>-0.0001190383443244097</v>
+        <v>-6.653905931764404e-05</v>
       </c>
       <c r="BR6" t="n">
-        <v>-0.002412116849765594</v>
+        <v>-0.001308136954046266</v>
       </c>
       <c r="BS6" t="n">
-        <v>-0.004055869872701567</v>
+        <v>-0.004572934002121476</v>
       </c>
       <c r="BT6" t="n">
-        <v>-0.001168820025540682</v>
+        <v>-0.0004047967398884161</v>
       </c>
       <c r="BU6" t="n">
-        <v>-0.0009105354767227404</v>
+        <v>-0.006073881002157005</v>
       </c>
       <c r="BV6" t="n">
-        <v>-0.002083243531187321</v>
+        <v>-0.002637026187004249</v>
       </c>
       <c r="BW6" t="n">
-        <v>-0.003047936648666047</v>
+        <v>-0.002961532301655614</v>
       </c>
       <c r="BX6" t="n">
-        <v>4.66962482259109e-05</v>
+        <v>-0.0002648201773469999</v>
       </c>
       <c r="BY6" t="n">
-        <v>-0.0002161414255393151</v>
+        <v>1.833516685004754e-05</v>
       </c>
       <c r="BZ6" t="n">
-        <v>-0.0001722036440916258</v>
+        <v>-9.163132315620503e-06</v>
       </c>
       <c r="CA6" t="n">
         <v>0</v>
       </c>
       <c r="CB6" t="n">
-        <v>-4.378290724909583e-05</v>
+        <v>0.0004316735488505863</v>
       </c>
       <c r="CC6" t="n">
-        <v>-0.004973771526826221</v>
+        <v>-0.001919851333825179</v>
       </c>
       <c r="CD6" t="n">
         <v>0</v>
       </c>
       <c r="CE6" t="n">
-        <v>-0.0002122939341189012</v>
+        <v>-0.0001646848639686171</v>
       </c>
       <c r="CF6" t="n">
-        <v>-0.007532042931753519</v>
+        <v>-0.002347522750421454</v>
       </c>
       <c r="CG6" t="n">
-        <v>-0.003430684291125955</v>
+        <v>-0.004234010729840101</v>
       </c>
       <c r="CH6" t="n">
-        <v>-0.001304574879009596</v>
+        <v>-4.229245750123902e-05</v>
       </c>
       <c r="CI6" t="n">
-        <v>-0.001397090992175745</v>
+        <v>0.0001287350797084197</v>
       </c>
       <c r="CJ6" t="n">
-        <v>-0.004672780127738049</v>
+        <v>-0.00399043317301011</v>
       </c>
       <c r="CK6" t="n">
-        <v>-0.002353180523531848</v>
+        <v>-0.0008380937857503434</v>
       </c>
     </row>
     <row r="7">
@@ -2232,268 +2232,268 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0002128897491168568</v>
+        <v>-0.001646258503401321</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.001434331484947948</v>
+        <v>-0.001476731208628046</v>
       </c>
       <c r="E7" t="n">
-        <v>0.000764646713011613</v>
+        <v>-0.002109045598437343</v>
       </c>
       <c r="F7" t="n">
-        <v>5.736422623988657e-05</v>
+        <v>-0.0004775702393552462</v>
       </c>
       <c r="G7" t="n">
-        <v>6.550065823058833e-05</v>
+        <v>-0.000780604349692382</v>
       </c>
       <c r="H7" t="n">
-        <v>0.002536457630075328</v>
+        <v>0.00518617698996362</v>
       </c>
       <c r="I7" t="n">
-        <v>7.611799114577987e-05</v>
+        <v>0.0001210017567891963</v>
       </c>
       <c r="J7" t="n">
-        <v>0.000722889177207936</v>
+        <v>-0.002157702294339675</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0189718850580728</v>
+        <v>0.02044504117436453</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02509038122666332</v>
+        <v>0.02624735105089459</v>
       </c>
       <c r="M7" t="n">
-        <v>0.001936230028342567</v>
+        <v>0.000742780170078422</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.001580757571022279</v>
+        <v>0.0001908599292500869</v>
       </c>
       <c r="O7" t="n">
-        <v>0.00455801047783147</v>
+        <v>0.002712480942795575</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0104125893760924</v>
+        <v>0.01181683182801706</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.005539466967572082</v>
+        <v>0.006845987480185922</v>
       </c>
       <c r="R7" t="n">
-        <v>4.647340081234143e-05</v>
+        <v>-0.001044994571456759</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.001783321243384101</v>
+        <v>-0.001564433908829654</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0008369024090647548</v>
+        <v>-0.001523316155239607</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.000741451663130721</v>
+        <v>-0.00141334081710156</v>
       </c>
       <c r="V7" t="n">
-        <v>3.65842252241455e-05</v>
+        <v>3.579869718108309e-05</v>
       </c>
       <c r="W7" t="n">
-        <v>0.004590671139493146</v>
+        <v>0.0007993270848353829</v>
       </c>
       <c r="X7" t="n">
-        <v>0.001042731393954188</v>
+        <v>0.0007411638599757352</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.0006960087552468186</v>
+        <v>0.0001198837832501243</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.0006698209142919188</v>
+        <v>-0.0001618512728465637</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.001179850846365615</v>
+        <v>0.001164524301723735</v>
       </c>
       <c r="AB7" t="n">
-        <v>-5.777689204025661e-05</v>
+        <v>0.0003340857718765522</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.002637226628214373</v>
+        <v>0.003246330110991802</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.0007400446721294029</v>
+        <v>-0.0009953641239455135</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0.0002665547733109175</v>
+        <v>-0.001332255553559641</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0.0002667823911454536</v>
+        <v>0.002885870144011637</v>
       </c>
       <c r="AG7" t="n">
-        <v>-4.345461903642613e-08</v>
+        <v>0.0002732085607160428</v>
       </c>
       <c r="AH7" t="n">
-        <v>-0.0001169705425623391</v>
+        <v>0.0002390406404657319</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.0005087318310818822</v>
+        <v>0.002898438592700797</v>
       </c>
       <c r="AK7" t="n">
-        <v>-0.001904179360390146</v>
+        <v>-0.001389471610946808</v>
       </c>
       <c r="AL7" t="n">
-        <v>-5.670134224875501e-05</v>
+        <v>-0.0004580512695411432</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.0001522939438306114</v>
+        <v>0.0009878497889949877</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.001601648799496969</v>
+        <v>-0.0005335273616624003</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.001515652273696527</v>
+        <v>0.003992604745217704</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.0001830303512278919</v>
+        <v>0.0002485018215891477</v>
       </c>
       <c r="AQ7" t="n">
-        <v>-0.0004399126925638764</v>
+        <v>0.0004228428213390867</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.0008751049228856944</v>
+        <v>-0.0003229112384922461</v>
       </c>
       <c r="AS7" t="n">
-        <v>0.0002092846270928594</v>
+        <v>-0.002183342407340727</v>
       </c>
       <c r="AT7" t="n">
-        <v>0.00048990179050169</v>
+        <v>-0.001227851807710873</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.002516185768653439</v>
+        <v>0.0006783269176992901</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.0005026440161313872</v>
+        <v>-1.20774307237004e-05</v>
       </c>
       <c r="AW7" t="n">
-        <v>-1.75438596490829e-05</v>
+        <v>0.000311697836450342</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.0004579326944080808</v>
+        <v>0.0001141335403672783</v>
       </c>
       <c r="AY7" t="n">
-        <v>0.0006412106069154766</v>
+        <v>-0.0006814998326815647</v>
       </c>
       <c r="AZ7" t="n">
-        <v>-0.002201445878329667</v>
+        <v>-0.002280588947907902</v>
       </c>
       <c r="BA7" t="n">
-        <v>-0.002994170652389383</v>
+        <v>-0.001615430296510417</v>
       </c>
       <c r="BB7" t="n">
-        <v>-0.004829931972789109</v>
+        <v>-0.004745947198144173</v>
       </c>
       <c r="BC7" t="n">
-        <v>0.0004199677871246255</v>
+        <v>0.0004485160569227653</v>
       </c>
       <c r="BD7" t="n">
-        <v>-0.0009778614014356148</v>
+        <v>0.000208454949483422</v>
       </c>
       <c r="BE7" t="n">
-        <v>-0.0003623670811708612</v>
+        <v>-3.756731339134012e-05</v>
       </c>
       <c r="BF7" t="n">
-        <v>-0.0001727929421978857</v>
+        <v>-0.001118521934628436</v>
       </c>
       <c r="BG7" t="n">
-        <v>-0.001616634266166355</v>
+        <v>0.0008294194390084998</v>
       </c>
       <c r="BH7" t="n">
         <v>0</v>
       </c>
       <c r="BI7" t="n">
-        <v>5.500550055003717e-05</v>
+        <v>-6.005270423308785e-05</v>
       </c>
       <c r="BJ7" t="n">
-        <v>-0.003168871348316748</v>
+        <v>-0.0005099428444195919</v>
       </c>
       <c r="BK7" t="n">
-        <v>-0.008017101209863898</v>
+        <v>-0.0009749290718545358</v>
       </c>
       <c r="BL7" t="n">
-        <v>-0.0001428657852731829</v>
+        <v>-0.0001277838627235684</v>
       </c>
       <c r="BM7" t="n">
-        <v>-0.001250190681486096</v>
+        <v>-0.000263868872619627</v>
       </c>
       <c r="BN7" t="n">
-        <v>-0.002923778789383269</v>
+        <v>-0.002445761730834445</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.0005503344885951834</v>
+        <v>0.000372242487406621</v>
       </c>
       <c r="BP7" t="n">
-        <v>-0.003398968719908091</v>
+        <v>-0.0007973136191814502</v>
       </c>
       <c r="BQ7" t="n">
-        <v>8.930191264739928e-05</v>
+        <v>-3.805900384051819e-05</v>
       </c>
       <c r="BR7" t="n">
-        <v>0.001955603293949159</v>
+        <v>-0.0005698090765278885</v>
       </c>
       <c r="BS7" t="n">
-        <v>-0.001415425018508926</v>
+        <v>-7.092226629594196e-05</v>
       </c>
       <c r="BT7" t="n">
-        <v>-0.0006246200434308347</v>
+        <v>-7.159251941000755e-05</v>
       </c>
       <c r="BU7" t="n">
-        <v>0.005518231985141853</v>
+        <v>-5.809352865093764e-06</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.0002168567733966509</v>
+        <v>-0.001388242032013498</v>
       </c>
       <c r="BW7" t="n">
-        <v>0.001168514287326161</v>
+        <v>0.001632029233763915</v>
       </c>
       <c r="BX7" t="n">
-        <v>9.305725093053385e-05</v>
+        <v>-7.889705768063804e-05</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.0001447267167813404</v>
+        <v>0.0003482541189683996</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0.0006329579388101858</v>
+        <v>0.000595247543611821</v>
       </c>
       <c r="CA7" t="n">
         <v>0</v>
       </c>
       <c r="CB7" t="n">
-        <v>0.0004985869386475051</v>
+        <v>0.0008402780917361242</v>
       </c>
       <c r="CC7" t="n">
-        <v>0.0008549248499147067</v>
+        <v>6.548906512859323e-05</v>
       </c>
       <c r="CD7" t="n">
         <v>0</v>
       </c>
       <c r="CE7" t="n">
-        <v>9.480470231320592e-05</v>
+        <v>0.0008180547377830527</v>
       </c>
       <c r="CF7" t="n">
-        <v>-0.0007081486257757341</v>
+        <v>-0.0006876205347907449</v>
       </c>
       <c r="CG7" t="n">
-        <v>-0.0006748751798256903</v>
+        <v>0.0001120924064931471</v>
       </c>
       <c r="CH7" t="n">
-        <v>-0.0004091770951839324</v>
+        <v>0.0005628147848798671</v>
       </c>
       <c r="CI7" t="n">
-        <v>3.899921739142779e-05</v>
+        <v>0.00231110710616001</v>
       </c>
       <c r="CJ7" t="n">
-        <v>0.001195311838876179</v>
+        <v>-0.001121426111069418</v>
       </c>
       <c r="CK7" t="n">
-        <v>-0.0008625028397185985</v>
+        <v>0.0009697970677931267</v>
       </c>
     </row>
     <row r="8">
@@ -2503,268 +2503,268 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.002236842105263192</v>
+        <v>0.0003589237515039756</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>0.002034822504414164</v>
+        <v>0.003061163478857948</v>
       </c>
       <c r="E8" t="n">
-        <v>0.002129597005064984</v>
+        <v>0.0006611561642814096</v>
       </c>
       <c r="F8" t="n">
-        <v>0.003669807446564958</v>
+        <v>0.007303501020773922</v>
       </c>
       <c r="G8" t="n">
-        <v>0.004739015738308491</v>
+        <v>0.002982315949691591</v>
       </c>
       <c r="H8" t="n">
-        <v>0.00489209057529438</v>
+        <v>0.008017647294348475</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0002148227712137546</v>
+        <v>0.0005518228324413177</v>
       </c>
       <c r="J8" t="n">
-        <v>0.006685430718087687</v>
+        <v>0.0005751801424030395</v>
       </c>
       <c r="K8" t="n">
-        <v>0.03862260613816481</v>
+        <v>0.02836569680157506</v>
       </c>
       <c r="L8" t="n">
-        <v>0.04076292441530838</v>
+        <v>0.04502559957722618</v>
       </c>
       <c r="M8" t="n">
-        <v>0.003742783265812316</v>
+        <v>0.004778950525163327</v>
       </c>
       <c r="N8" t="n">
-        <v>0.00071694882798857</v>
+        <v>0.004483295764492232</v>
       </c>
       <c r="O8" t="n">
-        <v>0.005291272697468894</v>
+        <v>0.006283555431304988</v>
       </c>
       <c r="P8" t="n">
-        <v>0.02048370300138333</v>
+        <v>0.01684566792407644</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.008699824144690546</v>
+        <v>0.01329757251278339</v>
       </c>
       <c r="R8" t="n">
-        <v>0.002030885477211711</v>
+        <v>0.00105442039170823</v>
       </c>
       <c r="S8" t="n">
-        <v>0.001246926672068569</v>
+        <v>-0.001091723441181058</v>
       </c>
       <c r="T8" t="n">
-        <v>0.004004348771472013</v>
+        <v>0.002346074490736627</v>
       </c>
       <c r="U8" t="n">
-        <v>0.001373727885981313</v>
+        <v>0.002022606783777339</v>
       </c>
       <c r="V8" t="n">
-        <v>0.0002371024953526452</v>
+        <v>0.0003305034644217164</v>
       </c>
       <c r="W8" t="n">
-        <v>0.01089269029642688</v>
+        <v>0.006325671337742369</v>
       </c>
       <c r="X8" t="n">
-        <v>0.004020751904541947</v>
+        <v>0.003492131382371397</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.001655454006939147</v>
+        <v>0.002064173575035031</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.00159101093876618</v>
+        <v>0.0002991964570238564</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.001495908362766121</v>
+        <v>0.002754566210045653</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.0004456855942004484</v>
+        <v>0.0008732368824051012</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.006745195280109959</v>
+        <v>0.01023285963318635</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.002784798903844629</v>
+        <v>0.001307741695671316</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.001674266775835315</v>
+        <v>0.002373790837502493</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.003108060600137844</v>
+        <v>0.008137012953012512</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.0007593164569977384</v>
+        <v>0.0005223332584187613</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.0005142429515657493</v>
+        <v>0.0006575049364990371</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.004153479527748918</v>
+        <v>0.007315672325547418</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.001135231445061929</v>
+        <v>0.006154111865136785</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.0005139595066683905</v>
+        <v>-0.0001305687737247652</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.0008218862295156838</v>
+        <v>0.001256549384041461</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.002567720495778666</v>
+        <v>0.0034640605100488</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.003404083297977078</v>
+        <v>0.004687869276256998</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.0007191161570007016</v>
+        <v>0.0007705391174454763</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.0007938980200596802</v>
+        <v>0.002213361059848743</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.004983992375141097</v>
+        <v>0.003539027679457743</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.0006446829612111154</v>
+        <v>-0.0009794465431297973</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.002062706270627037</v>
+        <v>0.002620036459832531</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.006213221008129049</v>
+        <v>0.001899805365151913</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.002863798660567823</v>
+        <v>0.001070002642759882</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.005789685940414385</v>
+        <v>0.001779565334813738</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.0005382150542720038</v>
+        <v>0.0004811125815514017</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.002924876378851246</v>
+        <v>0.0003402427301129551</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.0007433150393583637</v>
+        <v>0.0004818899810342808</v>
       </c>
       <c r="BA8" t="n">
-        <v>0.004301973444015325</v>
+        <v>-0.0003519038035412592</v>
       </c>
       <c r="BB8" t="n">
-        <v>0.002590532127190845</v>
+        <v>0.0003253898264320181</v>
       </c>
       <c r="BC8" t="n">
-        <v>0.001259191708644519</v>
+        <v>0.00142394408695099</v>
       </c>
       <c r="BD8" t="n">
-        <v>-6.65543785421524e-05</v>
+        <v>0.0008589225484557733</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.0001369112814896101</v>
+        <v>8.56164383561675e-05</v>
       </c>
       <c r="BF8" t="n">
-        <v>0.003179145233078781</v>
+        <v>0.001160419389219244</v>
       </c>
       <c r="BG8" t="n">
-        <v>0.005971810570178338</v>
+        <v>0.003928413439992254</v>
       </c>
       <c r="BH8" t="n">
         <v>0</v>
       </c>
       <c r="BI8" t="n">
-        <v>0.0002867866607928482</v>
+        <v>0.0001880449705949056</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.0003355803354431281</v>
+        <v>0.001349632639987214</v>
       </c>
       <c r="BK8" t="n">
-        <v>-0.002900040352798722</v>
+        <v>0.003747952673985799</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.0004683541032578759</v>
+        <v>0.0006023738932969619</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.00131007387239494</v>
+        <v>0.002220670169367773</v>
       </c>
       <c r="BN8" t="n">
-        <v>0.00167564601687234</v>
+        <v>0.005222701757355208</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.004101191195644093</v>
+        <v>0.001424320265104634</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.00140205927179757</v>
+        <v>0.002427200551380479</v>
       </c>
       <c r="BQ8" t="n">
-        <v>0.0001712441525065944</v>
+        <v>0.0001051667633985231</v>
       </c>
       <c r="BR8" t="n">
-        <v>0.007592649139234261</v>
+        <v>0.0003851538297822532</v>
       </c>
       <c r="BS8" t="n">
-        <v>-9.82686727772214e-05</v>
+        <v>0.004488581388259342</v>
       </c>
       <c r="BT8" t="n">
-        <v>0.0008326857018511963</v>
+        <v>0.002148197886990499</v>
       </c>
       <c r="BU8" t="n">
-        <v>0.0111365864418949</v>
+        <v>0.01009462901643449</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.003068101720425281</v>
+        <v>0.002770536394298767</v>
       </c>
       <c r="BW8" t="n">
-        <v>0.006777282944059002</v>
+        <v>0.007782621265539541</v>
       </c>
       <c r="BX8" t="n">
-        <v>0.0001601069047666631</v>
+        <v>1.893209156122177e-05</v>
       </c>
       <c r="BY8" t="n">
-        <v>0.001557868947228394</v>
+        <v>0.0008751178895043149</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0.001474411139744075</v>
+        <v>0.001148025726513427</v>
       </c>
       <c r="CA8" t="n">
-        <v>2.631578947368263e-05</v>
+        <v>0</v>
       </c>
       <c r="CB8" t="n">
-        <v>0.0008692560400613281</v>
+        <v>0.001370192589933766</v>
       </c>
       <c r="CC8" t="n">
-        <v>0.009341086777437557</v>
+        <v>0.004905645064313333</v>
       </c>
       <c r="CD8" t="n">
         <v>0</v>
       </c>
       <c r="CE8" t="n">
-        <v>0.001501123235585874</v>
+        <v>0.002069433336962836</v>
       </c>
       <c r="CF8" t="n">
-        <v>0.002756004530076489</v>
+        <v>0.004524820815817024</v>
       </c>
       <c r="CG8" t="n">
-        <v>0.003844346098181855</v>
+        <v>0.004073595496713747</v>
       </c>
       <c r="CH8" t="n">
-        <v>0.001281995187048798</v>
+        <v>0.0009392813789123934</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.005144904978766768</v>
+        <v>0.003716015264063208</v>
       </c>
       <c r="CJ8" t="n">
-        <v>0.004683519342969236</v>
+        <v>0.005596460734687258</v>
       </c>
       <c r="CK8" t="n">
-        <v>0.001051060746368041</v>
+        <v>0.002338694529542798</v>
       </c>
     </row>
     <row r="9">
@@ -2774,268 +2774,268 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.007925673113386367</v>
+        <v>0.002047781569965901</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0.01004767143381002</v>
+        <v>0.008447488584474871</v>
       </c>
       <c r="E9" t="n">
-        <v>0.007773985589685173</v>
+        <v>0.003234398782343983</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01563265306122446</v>
+        <v>0.01122448979591842</v>
       </c>
       <c r="G9" t="n">
-        <v>0.006430745814307415</v>
+        <v>0.01073469387755105</v>
       </c>
       <c r="H9" t="n">
-        <v>0.006470137825421174</v>
+        <v>0.0126331811263318</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0006446719757299158</v>
+        <v>0.0008497489378138878</v>
       </c>
       <c r="J9" t="n">
-        <v>0.01081632653061224</v>
+        <v>0.007859649122807044</v>
       </c>
       <c r="K9" t="n">
-        <v>0.06464992389649921</v>
+        <v>0.04207920792079206</v>
       </c>
       <c r="L9" t="n">
-        <v>0.06240487062404865</v>
+        <v>0.07157534246575344</v>
       </c>
       <c r="M9" t="n">
-        <v>0.007102040816326516</v>
+        <v>0.01334693877551025</v>
       </c>
       <c r="N9" t="n">
-        <v>0.001712328767123239</v>
+        <v>0.009306122448979626</v>
       </c>
       <c r="O9" t="n">
-        <v>0.005915813424345784</v>
+        <v>0.01225114854517611</v>
       </c>
       <c r="P9" t="n">
-        <v>0.02749336367083802</v>
+        <v>0.03774885145482385</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.03493877551020406</v>
+        <v>0.02922448979591842</v>
       </c>
       <c r="R9" t="n">
-        <v>0.006238113351084029</v>
+        <v>0.006930693069306914</v>
       </c>
       <c r="S9" t="n">
-        <v>0.002957906712172864</v>
+        <v>0.00470175438596494</v>
       </c>
       <c r="T9" t="n">
-        <v>0.006334492081884868</v>
+        <v>0.01453061224489802</v>
       </c>
       <c r="U9" t="n">
-        <v>0.006408797876374617</v>
+        <v>0.003843226788432275</v>
       </c>
       <c r="V9" t="n">
-        <v>0.0008067473414007708</v>
+        <v>0.0004569687738004369</v>
       </c>
       <c r="W9" t="n">
-        <v>0.01347368421052635</v>
+        <v>0.01277967387182409</v>
       </c>
       <c r="X9" t="n">
-        <v>0.01534693877551018</v>
+        <v>0.01473469387755108</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.003012746234067187</v>
+        <v>0.003707995365005834</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.00284414106939701</v>
+        <v>0.0033130236100533</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.00583673469387751</v>
+        <v>0.006738131699846839</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.001131799926980681</v>
+        <v>0.00118367346938778</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.01411182959300111</v>
+        <v>0.01657186196435347</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.01497959183673467</v>
+        <v>0.01914285714285719</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.01530612244897955</v>
+        <v>0.01346938775510209</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.01995918367346937</v>
+        <v>0.01289795918367351</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.00131434830230015</v>
+        <v>0.001293759512937587</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.001971937808115243</v>
+        <v>0.001668562760712944</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.01608163265306119</v>
+        <v>0.01518367346938782</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.02044897959183671</v>
+        <v>0.01044897959183678</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.0007667031763417653</v>
+        <v>0.0009520182787509102</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.001365187713310534</v>
+        <v>0.002701674277016741</v>
       </c>
       <c r="AN9" t="n">
-        <v>0.004112718964204143</v>
+        <v>0.004491228070175446</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.01146938775510202</v>
+        <v>0.008326530612244965</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.003271205781665998</v>
+        <v>0.001760176017601778</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.009387605427209345</v>
+        <v>0.004379284082254353</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.01416326530612242</v>
+        <v>0.009510204081632678</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.001637471439451643</v>
+        <v>0.0005327245053272534</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.006912280701754392</v>
+        <v>0.004642313546423127</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.01332603139832057</v>
+        <v>0.01702040816326537</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.003450891164201686</v>
+        <v>0.001510204081632693</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.008244897959183661</v>
+        <v>0.01323473644292759</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.0008800880088008278</v>
+        <v>0.0007996953541507645</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.01197373503283117</v>
+        <v>0.004000000000000048</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.008948971820258977</v>
+        <v>0.0111195734958111</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.007531380753138073</v>
+        <v>0.00617013508579779</v>
       </c>
       <c r="BB9" t="n">
-        <v>0.005366922234392136</v>
+        <v>0.003176341730558663</v>
       </c>
       <c r="BC9" t="n">
-        <v>0.00310332238043084</v>
+        <v>0.002437166793602441</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.001265306122448995</v>
+        <v>0.003215926493108701</v>
       </c>
       <c r="BE9" t="n">
+        <v>0.001099734546833564</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>0.004287901990811627</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>0.01066082511865649</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>0.0003650967506390046</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>0.002833078101071951</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>0.004398938187334123</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>0.008266970041714106</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>0.003462709284627108</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>0.01076981418278349</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>0.01000365096750645</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>0.008897959183673509</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>0.005802047781570008</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>0.001387755102040833</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>0.00342726580350341</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>0.007387755102040905</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>0.003226989365603239</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>0.02416326530612252</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>0.005832367709540398</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>0.01465306122448986</v>
+      </c>
+      <c r="BX9" t="n">
         <v>0.0004210526315789554</v>
       </c>
-      <c r="BF9" t="n">
-        <v>0.008470244614822963</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>0.01118367346938773</v>
-      </c>
-      <c r="BH9" t="n">
+      <c r="BY9" t="n">
+        <v>0.002246763137852215</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>0.002703731911652685</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>0.0001632653061224509</v>
+      </c>
+      <c r="CB9" t="n">
+        <v>0.00280621918847177</v>
+      </c>
+      <c r="CC9" t="n">
+        <v>0.01616326530612252</v>
+      </c>
+      <c r="CD9" t="n">
         <v>0</v>
       </c>
-      <c r="BI9" t="n">
-        <v>0.0009857612267251015</v>
-      </c>
-      <c r="BJ9" t="n">
-        <v>0.007444077741107402</v>
-      </c>
-      <c r="BK9" t="n">
-        <v>0.003157093952072998</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>0.0009132420091323646</v>
-      </c>
-      <c r="BM9" t="n">
-        <v>0.003102040816326523</v>
-      </c>
-      <c r="BN9" t="n">
-        <v>0.004754659566375008</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>0.0134801081498648</v>
-      </c>
-      <c r="BP9" t="n">
-        <v>0.009252938945771672</v>
-      </c>
-      <c r="BQ9" t="n">
-        <v>0.0002297090352220921</v>
-      </c>
-      <c r="BR9" t="n">
-        <v>0.01452408039438752</v>
-      </c>
-      <c r="BS9" t="n">
-        <v>0.005991657186196386</v>
-      </c>
-      <c r="BT9" t="n">
-        <v>0.004693802713604667</v>
-      </c>
-      <c r="BU9" t="n">
-        <v>0.01920408908360718</v>
-      </c>
-      <c r="BV9" t="n">
-        <v>0.00799536500579372</v>
-      </c>
-      <c r="BW9" t="n">
-        <v>0.01983673469387752</v>
-      </c>
-      <c r="BX9" t="n">
-        <v>0.0007346938775510293</v>
-      </c>
-      <c r="BY9" t="n">
-        <v>0.00443686006825933</v>
-      </c>
-      <c r="BZ9" t="n">
-        <v>0.003450891164201697</v>
-      </c>
-      <c r="CA9" t="n">
-        <v>0.000380517503805089</v>
-      </c>
-      <c r="CB9" t="n">
-        <v>0.003249361080686419</v>
-      </c>
-      <c r="CC9" t="n">
-        <v>0.01843003412969279</v>
-      </c>
-      <c r="CD9" t="n">
-        <v>0.0005111354508945398</v>
-      </c>
       <c r="CE9" t="n">
-        <v>0.005224489795918319</v>
+        <v>0.003922315308453894</v>
       </c>
       <c r="CF9" t="n">
-        <v>0.006448979591836712</v>
+        <v>0.01094946401225114</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.006326530612244874</v>
+        <v>0.009265306122449024</v>
       </c>
       <c r="CH9" t="n">
-        <v>0.001789794364051822</v>
+        <v>0.001901863826550054</v>
       </c>
       <c r="CI9" t="n">
-        <v>0.009061224489795905</v>
+        <v>0.007836734693877623</v>
       </c>
       <c r="CJ9" t="n">
-        <v>0.01171786120591578</v>
+        <v>0.01161007667031767</v>
       </c>
       <c r="CK9" t="n">
-        <v>0.002641653905053653</v>
+        <v>0.005537220388705566</v>
       </c>
     </row>
   </sheetData>
